--- a/numerical-workflows/v2/framework/经济/模块产销表/21_抽卡_概率.xlsx
+++ b/numerical-workflows/v2/framework/经济/模块产销表/21_抽卡_概率.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="卡池总览" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="品质概率" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="保底规则" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="权重曲线" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="自选池" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卡池总览" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质概率" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底规则" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权重曲线" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自选池" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'卡池总览'!$A$1:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'卡池总览'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'品质概率'!$A$1:$N$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'保底规则'!$A$1:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'保底规则'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'权重曲线'!$A$1:$C$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'自选池'!$A$1:$E$3</definedName>
   </definedNames>
@@ -187,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_gacha_overview" displayName="T_gacha_overview" ref="A1:N8" headerRowCount="1">
-  <autoFilter ref="A1:N8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_gacha_overview" displayName="T_gacha_overview" ref="A1:N6" headerRowCount="1">
+  <autoFilter ref="A1:N6"/>
   <tableColumns count="14">
     <tableColumn id="1" name="抽卡ID"/>
     <tableColumn id="2" name="卡池名"/>
@@ -233,8 +233,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_gacha_guarantee" displayName="T_gacha_guarantee" ref="A1:N8" headerRowCount="1">
-  <autoFilter ref="A1:N8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_gacha_guarantee" displayName="T_gacha_guarantee" ref="A1:N6" headerRowCount="1">
+  <autoFilter ref="A1:N6"/>
   <tableColumns count="14">
     <tableColumn id="1" name="抽卡ID"/>
     <tableColumn id="2" name="卡池名"/>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -810,11 +810,7 @@
           <t>DCT_Hero_NewPlayer</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
           <t>10</t>
@@ -870,11 +866,7 @@
           <t>DCT_Hero_Normal</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -913,7 +905,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>酒渍青锋</t>
+          <t>守望之刃</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -926,11 +918,7 @@
           <t>DCT_Hero_LimitTime</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -959,7 +947,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>311005</t>
+          <t>311006</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -976,48 +964,44 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>应许之邀</t>
+          <t>异象辑录</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>ExcWeapon</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>DCT_Hero_Choose</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>DCT_ExcWeapon_Normal</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr"/>
@@ -1025,19 +1009,19 @@
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>正式:Activity/DrawCard/DrawCard.xlsx#8</t>
+          <t>正式:Activity/DrawCard/DrawCard.xlsx#9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>异象辑录</t>
+          <t>醉眼朦胧</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1047,28 +1031,24 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>DCT_ExcWeapon_Normal</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>DCT_ExcWeapon_LimitTime</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1076,141 +1056,29 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>51002</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>正式:Activity/DrawCard/DrawCard.xlsx#9</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>醉眼朦胧</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>ExcWeapon</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>DCT_ExcWeapon_LimitTime</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>51002</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
           <t>正式:Activity/DrawCard/DrawCard.xlsx#10</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>自选名录</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>ExcWeapon</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>DCT_ExcWeapon_Choose</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>正式:Activity/DrawCard/DrawCard.xlsx#11</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1333,7 +1201,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -1358,11 +1226,7 @@
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#5</t>
@@ -1387,7 +1251,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -1396,14 +1260,14 @@
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.666667</v>
+        <v>0.909091</v>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>1001；1002；1011；1012；1014；1015；1018；1020；1021；1023；1024；1026；1029；1030；1040</t>
+          <t>1001；1002；1012；1018；1020；1021；1023；1024；1026；1030；1040</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -1412,11 +1276,7 @@
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M3" s="5" t="inlineStr"/>
       <c r="N3" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#6</t>
@@ -1441,7 +1301,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -1457,7 +1317,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>1003；1006；1017</t>
+          <t>1004；1005；1015</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -1466,11 +1326,7 @@
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#7</t>
@@ -1495,7 +1351,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -1520,11 +1376,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#8</t>
@@ -1549,7 +1401,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -1558,14 +1410,14 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.666667</v>
+        <v>0.909091</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>1001；1002；1011；1012；1014；1015；1018；1020；1021；1023；1024；1026；1029；1030；1040</t>
+          <t>1001；1002；1012；1018；1020；1021；1023；1024；1026；1030；1040</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -1574,11 +1426,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#9</t>
@@ -1603,7 +1451,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -1612,14 +1460,14 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.142857</v>
+        <v>0.090909</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>1003；1004；1006；1007；1008；1013；1017</t>
+          <t>1003；1004；1005；1007；1008；1011；1013；1014；1015；1017；1029</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1628,11 +1476,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M7" s="5" t="inlineStr"/>
       <c r="N7" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#10</t>
@@ -1652,12 +1496,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>酒渍青锋</t>
+          <t>守望之刃</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -1682,11 +1526,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#11</t>
@@ -1706,12 +1546,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>酒渍青锋</t>
+          <t>守望之刃</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
@@ -1720,14 +1560,14 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.666667</v>
+        <v>0.909091</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>1001；1002；1011；1012；1014；1015；1018；1020；1021；1023；1024；1026；1029；1030；1040</t>
+          <t>1001；1002；1012；1018；1020；1021；1023；1024；1026；1030；1040</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -1736,11 +1576,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#12</t>
@@ -1760,12 +1596,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>酒渍青锋</t>
+          <t>守望之刃</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
@@ -1773,19 +1609,19 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.125</v>
+        <v>0.083333</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>1005；1003；1004；1006；1007；1008；1013；1017</t>
+          <t>1006；1003；1004；1005；1007；1008；1011；1013；1014；1015；1017；1029</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1794,11 +1630,7 @@
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M10" s="5" t="inlineStr"/>
       <c r="N10" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#13</t>
@@ -1816,14 +1648,10 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>应许之邀</t>
-        </is>
-      </c>
+      <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -1848,11 +1676,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#14</t>
@@ -1870,14 +1694,10 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>应许之邀</t>
-        </is>
-      </c>
+      <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -1886,14 +1706,14 @@
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.666667</v>
+        <v>0.909091</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>1001；1002；1011；1012；1014；1015；1018；1020；1021；1023；1024；1026；1029；1030；1040</t>
+          <t>1001；1002；1012；1018；1020；1021；1023；1024；1026；1030；1040</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1902,11 +1722,7 @@
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M12" s="5" t="inlineStr"/>
       <c r="N12" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#15</t>
@@ -1924,14 +1740,10 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>应许之邀</t>
-        </is>
-      </c>
+      <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
@@ -1940,14 +1752,14 @@
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.142857</v>
+        <v>0.090909</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>1003；1004；1006；1007；1008；1013；1017</t>
+          <t>1003；1004；1005；1007；1008；1011；1013；1014；1015；1017；1029</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1956,11 +1768,7 @@
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M13" s="5" t="inlineStr"/>
       <c r="N13" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#16</t>
@@ -1985,11 +1793,11 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
@@ -1997,7 +1805,7 @@
         <v>11</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>7.727273</v>
+        <v>7.272727</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
@@ -2006,15 +1814,11 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>R级收容基础获得概率：85%（当未触发保底规则时，下述收容均分基础出率）</t>
+          <t>B级收容物基础出率合计80%：其中整件6.0%、对应碎片74.0%。可获得的整件如下所示，对应碎片亦为抽取产出，相关概率说明详见“规则说明”。</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#17</t>
@@ -2039,11 +1843,11 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr"/>
@@ -2051,7 +1855,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.866667</v>
+        <v>1</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
@@ -2060,15 +1864,11 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>A级收容基础获得概率：13%（当未触发保底规则时，下述收容均分基础出率）</t>
+          <t>A级收容物基础出率合计15%：其中整件0.75%、对应碎片14.25%。可获得的整件如下所示，对应碎片亦为抽取产出，相关概率说明详见“规则说明”。</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M15" s="5" t="inlineStr"/>
       <c r="N15" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#18</t>
@@ -2093,11 +1893,11 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
@@ -2105,24 +1905,20 @@
         <v>6</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.333333</v>
+        <v>0.833333</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>51001；51003；51004；51005；51007；51009</t>
+          <t>51001；51002；51003；51004；51005；51013</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>S级收容基础获得概率：2%（当未触发保底规则时，下述收容均分基础出率）</t>
+          <t>S级收容物基础出率合计5%：其中整件0.25%、对应碎片4.75%。可获得的整件如下所示，对应碎片亦为抽取产出，相关概率说明详见“规则说明”。</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#19</t>
@@ -2147,7 +1943,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -2172,11 +1968,7 @@
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M17" s="5" t="inlineStr"/>
       <c r="N17" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#20</t>
@@ -2201,7 +1993,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -2226,11 +2018,7 @@
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#21</t>
@@ -2255,7 +2043,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
@@ -2284,11 +2072,7 @@
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M19" s="5" t="inlineStr"/>
       <c r="N19" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#22</t>
@@ -2306,14 +2090,10 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>自选名录</t>
-        </is>
-      </c>
+      <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -2338,11 +2118,7 @@
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M20" s="5" t="inlineStr"/>
       <c r="N20" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#23</t>
@@ -2360,14 +2136,10 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>自选名录</t>
-        </is>
-      </c>
+      <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -2392,11 +2164,7 @@
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#24</t>
@@ -2414,14 +2182,10 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>自选名录</t>
-        </is>
-      </c>
+      <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2446,11 +2210,7 @@
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawCardPool.xlsx#25</t>
@@ -2472,7 +2232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2581,7 +2341,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
@@ -2597,7 +2357,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr"/>
@@ -2633,7 +2393,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr"/>
@@ -2649,7 +2409,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
@@ -2675,7 +2435,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>酒渍青锋</t>
+          <t>守望之刃</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2685,7 +2445,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
@@ -2701,7 +2461,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -2711,7 +2471,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>311005</t>
+          <t>311006</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -2734,38 +2494,38 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>异象辑录</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>应许之邀</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr"/>
@@ -2773,41 +2533,41 @@
       <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>正式:Activity/DrawCard/DrawCard.xlsx#8</t>
+          <t>正式:Activity/DrawCard/DrawCard.xlsx#9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>异象辑录</t>
+          <t>醉眼朦胧</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2817,142 +2577,38 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>51002</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>正式:Activity/DrawCard/DrawCard.xlsx#9</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>醉眼朦胧</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>51002</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
           <t>正式:Activity/DrawCard/DrawCard.xlsx#10</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>自选名录</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>正式:Activity/DrawCard/DrawCard.xlsx#11</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4071,17 +3727,13 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>1003；1004；1006；1007；1008；1013；1017</t>
+          <t>1003；1004；1005；1007；1008；1013；1014；1015；1017</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="inlineStr"/>
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawSpecialChooseGacha.xlsx#5</t>
@@ -4096,17 +3748,13 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>51001；51003；51004；51005；51007；51009</t>
+          <t>51001；51002；51003；51004；51005；51013</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>正式:Activity/DrawCard/DrawSpecialChooseGacha.xlsx#6</t>
